--- a/artfynd/A 12320-2024 artfynd.xlsx
+++ b/artfynd/A 12320-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137059962</v>
       </c>
       <c r="B2" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12320-2024 artfynd.xlsx
+++ b/artfynd/A 12320-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137059962</v>
       </c>
       <c r="B2" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12320-2024 artfynd.xlsx
+++ b/artfynd/A 12320-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137059962</v>
       </c>
       <c r="B2" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12320-2024 artfynd.xlsx
+++ b/artfynd/A 12320-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137059962</v>
       </c>
       <c r="B2" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12320-2024 artfynd.xlsx
+++ b/artfynd/A 12320-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137059962</v>
       </c>
       <c r="B2" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12320-2024 artfynd.xlsx
+++ b/artfynd/A 12320-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137059962</v>
       </c>
       <c r="B2" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
